--- a/excel comparision test.xlsx
+++ b/excel comparision test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://norstellaglobal-my.sharepoint.com/personal/suneelkumar_yarramuthala_norstella_com/Documents/Documents/Zip files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7630D9F9-68D6-4FCF-BB92-305F5F28477F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{7630D9F9-68D6-4FCF-BB92-305F5F28477F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{889221AE-4007-4721-B24B-BA8617FF4EC0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{05369730-37D4-4A7A-9E54-5E409C215E59}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>ID</t>
   </si>
@@ -50,17 +50,32 @@
     <t>14/12/2025</t>
   </si>
   <si>
-    <t>15/12/2026</t>
+    <t>15/12/2025</t>
+  </si>
+  <si>
+    <t>16/12/2025</t>
+  </si>
+  <si>
+    <t>17/12/2025</t>
+  </si>
+  <si>
+    <t>18/12/2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -423,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6BA14C2-398B-4BE4-83D3-12FD65B406FA}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -477,7 +492,32 @@
         <v>4</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/excel comparision test.xlsx
+++ b/excel comparision test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://norstellaglobal-my.sharepoint.com/personal/suneelkumar_yarramuthala_norstella_com/Documents/Documents/Zip files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{7630D9F9-68D6-4FCF-BB92-305F5F28477F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{889221AE-4007-4721-B24B-BA8617FF4EC0}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{7630D9F9-68D6-4FCF-BB92-305F5F28477F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC5D3205-D355-458B-85D1-99B453A95E0E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{05369730-37D4-4A7A-9E54-5E409C215E59}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>ID</t>
   </si>
@@ -60,6 +60,15 @@
   </si>
   <si>
     <t>18/12/2025</t>
+  </si>
+  <si>
+    <t>19/12/2025</t>
+  </si>
+  <si>
+    <t>20/12/2025</t>
+  </si>
+  <si>
+    <t>21/12/2025</t>
   </si>
 </sst>
 </file>
@@ -438,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6BA14C2-398B-4BE4-83D3-12FD65B406FA}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -516,6 +525,30 @@
         <v>7</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
